--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/15.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/15.xlsx
@@ -426,13 +426,13 @@
         <v>-10.17974257818555</v>
       </c>
       <c r="E2">
-        <v>-14.89682941607394</v>
+        <v>-17.66221452444197</v>
       </c>
       <c r="F2">
-        <v>-3.55326224073832</v>
+        <v>-3.003617274693569</v>
       </c>
       <c r="G2">
-        <v>-15.47363500995282</v>
+        <v>-14.20635155642873</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-9.754081909498188</v>
       </c>
       <c r="E3">
-        <v>-15.78461863138168</v>
+        <v>-18.06250898434999</v>
       </c>
       <c r="F3">
-        <v>-3.466771571844621</v>
+        <v>-2.641830296623094</v>
       </c>
       <c r="G3">
-        <v>-14.83438356377448</v>
+        <v>-13.44919503086925</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.180718710538379</v>
       </c>
       <c r="E4">
-        <v>-15.85821991942835</v>
+        <v>-17.28570813849624</v>
       </c>
       <c r="F4">
-        <v>-3.147072284775582</v>
+        <v>-2.903359139565342</v>
       </c>
       <c r="G4">
-        <v>-14.88271918392061</v>
+        <v>-12.86116269000174</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-8.504048509556824</v>
       </c>
       <c r="E5">
-        <v>-16.13801168599226</v>
+        <v>-19.32265197493843</v>
       </c>
       <c r="F5">
-        <v>-3.176698844936707</v>
+        <v>-2.641180028211896</v>
       </c>
       <c r="G5">
-        <v>-14.92362262933107</v>
+        <v>-13.22615364625193</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-7.733821530656565</v>
       </c>
       <c r="E6">
-        <v>-17.77126923549469</v>
+        <v>-18.81683501370367</v>
       </c>
       <c r="F6">
-        <v>-3.075227151563378</v>
+        <v>-2.267183742991559</v>
       </c>
       <c r="G6">
-        <v>-15.25411604578929</v>
+        <v>-13.56293047814368</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-6.90623930099389</v>
       </c>
       <c r="E7">
-        <v>-17.53614633654243</v>
+        <v>-19.1642368972021</v>
       </c>
       <c r="F7">
-        <v>-2.683256122069694</v>
+        <v>-2.420271837600727</v>
       </c>
       <c r="G7">
-        <v>-14.62754564429913</v>
+        <v>-13.53634679746333</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-6.049103458355856</v>
       </c>
       <c r="E8">
-        <v>-18.61048603859616</v>
+        <v>-19.9637389832563</v>
       </c>
       <c r="F8">
-        <v>-2.738664789275551</v>
+        <v>-2.369983309311575</v>
       </c>
       <c r="G8">
-        <v>-14.9955574733539</v>
+        <v>-12.98760566632867</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-5.18733706636342</v>
       </c>
       <c r="E9">
-        <v>-18.44144263236383</v>
+        <v>-20.97392832251737</v>
       </c>
       <c r="F9">
-        <v>-2.891864713484097</v>
+        <v>-1.808399912257678</v>
       </c>
       <c r="G9">
-        <v>-14.14811409457464</v>
+        <v>-12.68184368032158</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-4.341261724891223</v>
       </c>
       <c r="E10">
-        <v>-19.54835111948072</v>
+        <v>-22.10580228683854</v>
       </c>
       <c r="F10">
-        <v>-2.634611074707696</v>
+        <v>-2.270324083815571</v>
       </c>
       <c r="G10">
-        <v>-13.61717211153187</v>
+        <v>-13.03389371405876</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-3.535890030156122</v>
       </c>
       <c r="E11">
-        <v>-20.40286963625411</v>
+        <v>-22.14445281249401</v>
       </c>
       <c r="F11">
-        <v>-2.335657420874369</v>
+        <v>-1.934095553591072</v>
       </c>
       <c r="G11">
-        <v>-13.44970816542784</v>
+        <v>-11.89211966301952</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-2.783840551723396</v>
       </c>
       <c r="E12">
-        <v>-21.12804587842042</v>
+        <v>-22.80605833654064</v>
       </c>
       <c r="F12">
-        <v>-2.151445077839814</v>
+        <v>-1.876813119320083</v>
       </c>
       <c r="G12">
-        <v>-13.72072266545473</v>
+        <v>-11.67598076585158</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-2.09130618879969</v>
       </c>
       <c r="E13">
-        <v>-21.3602343262157</v>
+        <v>-23.58035040779414</v>
       </c>
       <c r="F13">
-        <v>-2.213902323276092</v>
+        <v>-1.936595566412721</v>
       </c>
       <c r="G13">
-        <v>-12.66027216558769</v>
+        <v>-12.39450819078608</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-1.473776620900108</v>
       </c>
       <c r="E14">
-        <v>-22.54405441587886</v>
+        <v>-24.98553589237425</v>
       </c>
       <c r="F14">
-        <v>-2.282775274247051</v>
+        <v>-1.685291262323226</v>
       </c>
       <c r="G14">
-        <v>-12.53689144388459</v>
+        <v>-11.26607894881564</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-0.9330140221610146</v>
       </c>
       <c r="E15">
-        <v>-23.25894649357375</v>
+        <v>-25.68100534505025</v>
       </c>
       <c r="F15">
-        <v>-1.944653096139751</v>
+        <v>-1.551446970848493</v>
       </c>
       <c r="G15">
-        <v>-11.20554231308453</v>
+        <v>-11.01577853222796</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-0.4647167860544283</v>
       </c>
       <c r="E16">
-        <v>-23.98983766993774</v>
+        <v>-26.17339538085226</v>
       </c>
       <c r="F16">
-        <v>-1.673204553548979</v>
+        <v>-1.396914203488843</v>
       </c>
       <c r="G16">
-        <v>-11.26761504194586</v>
+        <v>-10.66948222663804</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-0.06814931991345154</v>
       </c>
       <c r="E17">
-        <v>-25.4784150033691</v>
+        <v>-27.22580368328683</v>
       </c>
       <c r="F17">
-        <v>-1.836197437193421</v>
+        <v>-1.118510688184165</v>
       </c>
       <c r="G17">
-        <v>-10.50796402032254</v>
+        <v>-10.1974348487389</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>0.2647863943908881</v>
       </c>
       <c r="E18">
-        <v>-25.77906039273833</v>
+        <v>-27.53728571095643</v>
       </c>
       <c r="F18">
-        <v>-1.491782151927053</v>
+        <v>-0.7943423589770237</v>
       </c>
       <c r="G18">
-        <v>-10.24056132547899</v>
+        <v>-9.576618175395993</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>0.5452766884736302</v>
       </c>
       <c r="E19">
-        <v>-26.56941496129704</v>
+        <v>-27.88830131671298</v>
       </c>
       <c r="F19">
-        <v>-1.481101182635357</v>
+        <v>-0.9904020126064162</v>
       </c>
       <c r="G19">
-        <v>-9.993763466071858</v>
+        <v>-9.429845138912404</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>0.7808636457864028</v>
       </c>
       <c r="E20">
-        <v>-26.70638318613303</v>
+        <v>-29.93647124022018</v>
       </c>
       <c r="F20">
-        <v>-1.019992124601817</v>
+        <v>-0.8128348328771199</v>
       </c>
       <c r="G20">
-        <v>-9.106275728449578</v>
+        <v>-8.84494457412505</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>0.9764912853867681</v>
       </c>
       <c r="E21">
-        <v>-27.07680330301246</v>
+        <v>-29.55475484492863</v>
       </c>
       <c r="F21">
-        <v>-0.9468737906915107</v>
+        <v>-0.3922528216581436</v>
       </c>
       <c r="G21">
-        <v>-9.139818175853474</v>
+        <v>-8.043421772521024</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>1.135909762899986</v>
       </c>
       <c r="E22">
-        <v>-27.63839295012568</v>
+        <v>-30.52010097032873</v>
       </c>
       <c r="F22">
-        <v>-0.9254223884286147</v>
+        <v>-0.4937236866640691</v>
       </c>
       <c r="G22">
-        <v>-9.69881372179603</v>
+        <v>-8.355943892519303</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>1.259698454112136</v>
       </c>
       <c r="E23">
-        <v>-28.94373916825868</v>
+        <v>-30.12894497096819</v>
       </c>
       <c r="F23">
-        <v>-0.6344276886013848</v>
+        <v>-0.6848297032247206</v>
       </c>
       <c r="G23">
-        <v>-9.163329670273377</v>
+        <v>-7.911996425157497</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>1.345385702662292</v>
       </c>
       <c r="E24">
-        <v>-29.94103820625692</v>
+        <v>-30.79836890538907</v>
       </c>
       <c r="F24">
-        <v>-0.7164567706636058</v>
+        <v>-0.351493003603394</v>
       </c>
       <c r="G24">
-        <v>-8.731399483219127</v>
+        <v>-7.513194867314732</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>1.391678510121345</v>
       </c>
       <c r="E25">
-        <v>-29.6660851141702</v>
+        <v>-30.82675790894315</v>
       </c>
       <c r="F25">
-        <v>-0.5114780852082709</v>
+        <v>-0.1437318320420556</v>
       </c>
       <c r="G25">
-        <v>-9.384480733387772</v>
+        <v>-8.444997567525697</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>1.397214903886942</v>
       </c>
       <c r="E26">
-        <v>-29.95857472185162</v>
+        <v>-30.41321539832569</v>
       </c>
       <c r="F26">
-        <v>-0.606897726336746</v>
+        <v>-0.1019655475929045</v>
       </c>
       <c r="G26">
-        <v>-8.776247443639633</v>
+        <v>-7.927102444453191</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>1.359411989556288</v>
       </c>
       <c r="E27">
-        <v>-30.43756953153894</v>
+        <v>-31.66550601498483</v>
       </c>
       <c r="F27">
-        <v>-0.4097968148820344</v>
+        <v>-0.06005264211345791</v>
       </c>
       <c r="G27">
-        <v>-8.798673079122656</v>
+        <v>-8.583904747807978</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>1.277356888965687</v>
       </c>
       <c r="E28">
-        <v>-30.23962087571566</v>
+        <v>-32.33462427741019</v>
       </c>
       <c r="F28">
-        <v>-0.6243381736352868</v>
+        <v>-0.4691543094970357</v>
       </c>
       <c r="G28">
-        <v>-8.910529791803551</v>
+        <v>-8.169666116115591</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>1.151781505518606</v>
       </c>
       <c r="E29">
-        <v>-29.02431430627716</v>
+        <v>-30.79644656817281</v>
       </c>
       <c r="F29">
-        <v>-0.228068745688476</v>
+        <v>-0.1616800685585125</v>
       </c>
       <c r="G29">
-        <v>-9.24989712557978</v>
+        <v>-8.013044206652671</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>0.9813972202424668</v>
       </c>
       <c r="E30">
-        <v>-29.38237621758965</v>
+        <v>-31.79929298683044</v>
       </c>
       <c r="F30">
-        <v>-0.2948119640668378</v>
+        <v>-0.02269327224720021</v>
       </c>
       <c r="G30">
-        <v>-9.01314677188434</v>
+        <v>-8.379299791298861</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>0.7652933568934565</v>
       </c>
       <c r="E31">
-        <v>-29.08494604476586</v>
+        <v>-31.23708520301517</v>
       </c>
       <c r="F31">
-        <v>-0.586508291084239</v>
+        <v>-0.273103767909074</v>
       </c>
       <c r="G31">
-        <v>-8.854793447104381</v>
+        <v>-8.762333220738077</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>0.5054546490824646</v>
       </c>
       <c r="E32">
-        <v>-28.96808424452392</v>
+        <v>-30.71123880124449</v>
       </c>
       <c r="F32">
-        <v>-0.5513507217746223</v>
+        <v>-0.2844209233661208</v>
       </c>
       <c r="G32">
-        <v>-9.079874127773889</v>
+        <v>-8.462341515605939</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>0.2002408573835449</v>
       </c>
       <c r="E33">
-        <v>-29.16931151552876</v>
+        <v>-30.65860887632734</v>
       </c>
       <c r="F33">
-        <v>-0.9275247848969198</v>
+        <v>-0.2435095140766588</v>
       </c>
       <c r="G33">
-        <v>-8.553255717205404</v>
+        <v>-7.81291179716711</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-0.1521635312844817</v>
       </c>
       <c r="E34">
-        <v>-28.78512030919201</v>
+        <v>-29.88639537464336</v>
       </c>
       <c r="F34">
-        <v>-0.7755251650550301</v>
+        <v>-0.2548216993292889</v>
       </c>
       <c r="G34">
-        <v>-8.757026416238624</v>
+        <v>-8.465913594242812</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-0.5509382067249653</v>
       </c>
       <c r="E35">
-        <v>-28.2061232079933</v>
+        <v>-29.18823600840681</v>
       </c>
       <c r="F35">
-        <v>-0.4638858928152309</v>
+        <v>-0.353550668231948</v>
       </c>
       <c r="G35">
-        <v>-8.550262984037904</v>
+        <v>-8.361763831577342</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.9968479656506312</v>
       </c>
       <c r="E36">
-        <v>-27.64213799813002</v>
+        <v>-29.54963087658895</v>
       </c>
       <c r="F36">
-        <v>-0.5838243806991685</v>
+        <v>-0.1859280391732596</v>
       </c>
       <c r="G36">
-        <v>-9.043143625015675</v>
+        <v>-8.824005373589159</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-1.491363598948325</v>
       </c>
       <c r="E37">
-        <v>-27.37879817763598</v>
+        <v>-28.87357499198384</v>
       </c>
       <c r="F37">
-        <v>-1.231264745583623</v>
+        <v>-0.4505466925279504</v>
       </c>
       <c r="G37">
-        <v>-9.221108621570277</v>
+        <v>-8.967308958347591</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.031575948412666</v>
       </c>
       <c r="E38">
-        <v>-27.53317385655746</v>
+        <v>-27.28494555382701</v>
       </c>
       <c r="F38">
-        <v>-0.6163129502369651</v>
+        <v>-0.2370383079259891</v>
       </c>
       <c r="G38">
-        <v>-9.886627591329963</v>
+        <v>-9.169033740237541</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.61097706720531</v>
       </c>
       <c r="E39">
-        <v>-26.22701704157708</v>
+        <v>-26.61938214349767</v>
       </c>
       <c r="F39">
-        <v>-0.611248311936249</v>
+        <v>0.04040678629364933</v>
       </c>
       <c r="G39">
-        <v>-8.855167538750319</v>
+        <v>-8.983298893302271</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.227039172317093</v>
       </c>
       <c r="E40">
-        <v>-25.76379490685848</v>
+        <v>-28.06056899643876</v>
       </c>
       <c r="F40">
-        <v>-0.6198053472071678</v>
+        <v>-0.1492413036380751</v>
       </c>
       <c r="G40">
-        <v>-9.504388692820173</v>
+        <v>-9.142430196283959</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.873040139791987</v>
       </c>
       <c r="E41">
-        <v>-25.29779228909916</v>
+        <v>-26.65923724323918</v>
       </c>
       <c r="F41">
-        <v>-0.5645739506255109</v>
+        <v>0.04345352160114591</v>
       </c>
       <c r="G41">
-        <v>-9.547045072093683</v>
+        <v>-8.637270741901029</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.533541301350319</v>
       </c>
       <c r="E42">
-        <v>-25.16373134457608</v>
+        <v>-25.24868551695998</v>
       </c>
       <c r="F42">
-        <v>-0.8860277198536786</v>
+        <v>0.007436106927423409</v>
       </c>
       <c r="G42">
-        <v>-10.26109663945909</v>
+        <v>-8.346237372998159</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-5.203345239479134</v>
       </c>
       <c r="E43">
-        <v>-24.13390201354375</v>
+        <v>-25.53487601729673</v>
       </c>
       <c r="F43">
-        <v>-0.6823918179582816</v>
+        <v>0.1889545991680735</v>
       </c>
       <c r="G43">
-        <v>-9.331233918934133</v>
+        <v>-8.827630420954661</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-5.873418678194041</v>
       </c>
       <c r="E44">
-        <v>-23.73659181800679</v>
+        <v>-25.51241478621868</v>
       </c>
       <c r="F44">
-        <v>-0.5613565716330375</v>
+        <v>0.1502317365568078</v>
       </c>
       <c r="G44">
-        <v>-10.11618744011411</v>
+        <v>-9.195018212175281</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-6.525554245720691</v>
       </c>
       <c r="E45">
-        <v>-23.65901000130738</v>
+        <v>-23.8909856108243</v>
       </c>
       <c r="F45">
-        <v>-0.252627354079273</v>
+        <v>0.3452691848111458</v>
       </c>
       <c r="G45">
-        <v>-9.586453806193166</v>
+        <v>-9.2819663802187</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-7.152336704684569</v>
       </c>
       <c r="E46">
-        <v>-21.41228460645986</v>
+        <v>-24.62155526553374</v>
       </c>
       <c r="F46">
-        <v>-0.5913061950812536</v>
+        <v>0.2215574834074564</v>
       </c>
       <c r="G46">
-        <v>-9.470045093395774</v>
+        <v>-9.796637031935955</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-7.746916845841741</v>
       </c>
       <c r="E47">
-        <v>-21.40442317558254</v>
+        <v>-22.78899957495375</v>
       </c>
       <c r="F47">
-        <v>-0.4179935103327355</v>
+        <v>0.03905323395747494</v>
       </c>
       <c r="G47">
-        <v>-9.796736348302133</v>
+        <v>-8.967643323447057</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-8.295926485869458</v>
       </c>
       <c r="E48">
-        <v>-20.85085798441091</v>
+        <v>-23.91195697395382</v>
       </c>
       <c r="F48">
-        <v>-0.3955629777997305</v>
+        <v>0.1814645011119604</v>
       </c>
       <c r="G48">
-        <v>-10.07855315842367</v>
+        <v>-8.976042177480188</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-8.789948618464912</v>
       </c>
       <c r="E49">
-        <v>-20.75324219870157</v>
+        <v>-21.97623811700509</v>
       </c>
       <c r="F49">
-        <v>-0.6454615424066741</v>
+        <v>0.0005739113626323052</v>
       </c>
       <c r="G49">
-        <v>-10.49809528406997</v>
+        <v>-9.222975769254425</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-9.227541757852855</v>
       </c>
       <c r="E50">
-        <v>-19.48412377262993</v>
+        <v>-21.89324930234052</v>
       </c>
       <c r="F50">
-        <v>-0.8535963076666752</v>
+        <v>-0.1201705780042292</v>
       </c>
       <c r="G50">
-        <v>-10.30707349590848</v>
+        <v>-9.399970775966022</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-9.600857019328119</v>
       </c>
       <c r="E51">
-        <v>-19.47325090653751</v>
+        <v>-21.04897419377248</v>
       </c>
       <c r="F51">
-        <v>-0.4583350028490714</v>
+        <v>0.1971140180856486</v>
       </c>
       <c r="G51">
-        <v>-11.05195948442666</v>
+        <v>-9.913012639277955</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-9.897891823466928</v>
       </c>
       <c r="E52">
-        <v>-17.64979744871293</v>
+        <v>-20.80258897996315</v>
       </c>
       <c r="F52">
-        <v>-0.3518467164843894</v>
+        <v>0.1990855325043114</v>
       </c>
       <c r="G52">
-        <v>-10.79336284071757</v>
+        <v>-9.322897965266248</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-10.12075872411206</v>
       </c>
       <c r="E53">
-        <v>-18.23661522452289</v>
+        <v>-19.00631542313261</v>
       </c>
       <c r="F53">
-        <v>-0.6727661887377514</v>
+        <v>0.3799578981707779</v>
       </c>
       <c r="G53">
-        <v>-11.10952987135458</v>
+        <v>-9.593492026009658</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-10.26503423904758</v>
       </c>
       <c r="E54">
-        <v>-17.87018922171823</v>
+        <v>-19.55375358897187</v>
       </c>
       <c r="F54">
-        <v>-0.6938158328102897</v>
+        <v>0.08629088510211674</v>
       </c>
       <c r="G54">
-        <v>-10.35747655174389</v>
+        <v>-9.559194774222808</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-10.31877400311238</v>
       </c>
       <c r="E55">
-        <v>-17.08102564182355</v>
+        <v>-19.41402299499119</v>
       </c>
       <c r="F55">
-        <v>-0.6650060429083257</v>
+        <v>0.02316928900879442</v>
       </c>
       <c r="G55">
-        <v>-11.12011368544363</v>
+        <v>-9.354394495526874</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-10.28713512195118</v>
       </c>
       <c r="E56">
-        <v>-17.65097032348092</v>
+        <v>-18.70187517254495</v>
       </c>
       <c r="F56">
-        <v>-0.9285602441504192</v>
+        <v>0.02156805481918297</v>
       </c>
       <c r="G56">
-        <v>-10.74910746794859</v>
+        <v>-9.788142172082186</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-10.17236721536049</v>
       </c>
       <c r="E57">
-        <v>-16.18057028471635</v>
+        <v>-18.58939240666843</v>
       </c>
       <c r="F57">
-        <v>-0.7807720441843622</v>
+        <v>0.2332407772565406</v>
       </c>
       <c r="G57">
-        <v>-11.01614269223728</v>
+        <v>-9.843199854945805</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-9.969757558811624</v>
       </c>
       <c r="E58">
-        <v>-15.74483145875029</v>
+        <v>-17.6540859135982</v>
       </c>
       <c r="F58">
-        <v>-1.147047945210608</v>
+        <v>-0.02793600953951828</v>
       </c>
       <c r="G58">
-        <v>-10.40188420960767</v>
+        <v>-9.787622416432519</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-9.684396699228714</v>
       </c>
       <c r="E59">
-        <v>-15.74389859310471</v>
+        <v>-17.38060683980098</v>
       </c>
       <c r="F59">
-        <v>-1.085304752475544</v>
+        <v>-0.01829795480794603</v>
       </c>
       <c r="G59">
-        <v>-10.51796186785114</v>
+        <v>-10.72997582527714</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-9.324822454147114</v>
       </c>
       <c r="E60">
-        <v>-14.2982693071621</v>
+        <v>-16.89727828048832</v>
       </c>
       <c r="F60">
-        <v>-0.6355020811228157</v>
+        <v>0.2020577147455561</v>
       </c>
       <c r="G60">
-        <v>-10.41982736643052</v>
+        <v>-10.05795825462387</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.893177961484618</v>
       </c>
       <c r="E61">
-        <v>-14.56747350149608</v>
+        <v>-16.90841379807317</v>
       </c>
       <c r="F61">
-        <v>-1.361571079880999</v>
+        <v>-0.1611316893378592</v>
       </c>
       <c r="G61">
-        <v>-11.01240177577791</v>
+        <v>-10.4848795862772</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.392688397262271</v>
       </c>
       <c r="E62">
-        <v>-15.23848466605664</v>
+        <v>-16.61753179866448</v>
       </c>
       <c r="F62">
-        <v>-0.940592280676082</v>
+        <v>-0.3348270798264707</v>
       </c>
       <c r="G62">
-        <v>-11.16866614632258</v>
+        <v>-10.1897974201798</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.838204058460652</v>
       </c>
       <c r="E63">
-        <v>-14.6658455423647</v>
+        <v>-17.07744814735749</v>
       </c>
       <c r="F63">
-        <v>-1.158155523714747</v>
+        <v>-0.5531292265884329</v>
       </c>
       <c r="G63">
-        <v>-10.95196445641297</v>
+        <v>-10.61591097872155</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.235584441368454</v>
       </c>
       <c r="E64">
-        <v>-14.93094693924773</v>
+        <v>-16.51033829042891</v>
       </c>
       <c r="F64">
-        <v>-1.163868773691855</v>
+        <v>-0.5517359126169241</v>
       </c>
       <c r="G64">
-        <v>-10.60237415801147</v>
+        <v>-10.5034848522079</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-6.587274600427345</v>
       </c>
       <c r="E65">
-        <v>-14.25831458099242</v>
+        <v>-16.12539082893289</v>
       </c>
       <c r="F65">
-        <v>-1.664858751965774</v>
+        <v>-0.4418504915333613</v>
       </c>
       <c r="G65">
-        <v>-11.19859016745206</v>
+        <v>-10.82267772146781</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.908446433851131</v>
       </c>
       <c r="E66">
-        <v>-13.31110272975603</v>
+        <v>-16.73005532080707</v>
       </c>
       <c r="F66">
-        <v>-1.333921004342954</v>
+        <v>-0.3923745916663552</v>
       </c>
       <c r="G66">
-        <v>-10.49006059004616</v>
+        <v>-10.90905647567848</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.205178779173857</v>
       </c>
       <c r="E67">
-        <v>-13.23689462619233</v>
+        <v>-15.72979692504483</v>
       </c>
       <c r="F67">
-        <v>-1.465233805034732</v>
+        <v>-0.6055905625751283</v>
       </c>
       <c r="G67">
-        <v>-10.99730899866437</v>
+        <v>-10.534388794817</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.480142514779573</v>
       </c>
       <c r="E68">
-        <v>-14.38096377101616</v>
+        <v>-15.84993734046832</v>
       </c>
       <c r="F68">
-        <v>-1.611683363277865</v>
+        <v>-0.6141161198847408</v>
       </c>
       <c r="G68">
-        <v>-10.76084666243085</v>
+        <v>-10.49319567667185</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-3.739941736485565</v>
       </c>
       <c r="E69">
-        <v>-13.45080615289266</v>
+        <v>-15.85738668021094</v>
       </c>
       <c r="F69">
-        <v>-1.530749382922145</v>
+        <v>-0.6574794966864893</v>
       </c>
       <c r="G69">
-        <v>-10.88848474569745</v>
+        <v>-9.961621379431074</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-2.987005084782693</v>
       </c>
       <c r="E70">
-        <v>-14.28813458233293</v>
+        <v>-14.76267790207071</v>
       </c>
       <c r="F70">
-        <v>-1.892528077318593</v>
+        <v>-1.188783580065856</v>
       </c>
       <c r="G70">
-        <v>-10.2625896954973</v>
+        <v>-9.941672032011427</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-2.22098085008207</v>
       </c>
       <c r="E71">
-        <v>-14.36683946058624</v>
+        <v>-15.10162965307083</v>
       </c>
       <c r="F71">
-        <v>-1.768438640379227</v>
+        <v>-1.147054572149831</v>
       </c>
       <c r="G71">
-        <v>-10.92998574457775</v>
+        <v>-9.878632623852624</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-1.440404881145507</v>
       </c>
       <c r="E72">
-        <v>-14.34684624784238</v>
+        <v>-15.83853464291701</v>
       </c>
       <c r="F72">
-        <v>-1.606973266225547</v>
+        <v>-1.088557751266338</v>
       </c>
       <c r="G72">
-        <v>-10.11554850482503</v>
+        <v>-9.748415625610932</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-0.6451379482938027</v>
       </c>
       <c r="E73">
-        <v>-14.47522848595983</v>
+        <v>-16.24379683881144</v>
       </c>
       <c r="F73">
-        <v>-1.888283522746648</v>
+        <v>-0.700234851814583</v>
       </c>
       <c r="G73">
-        <v>-10.10283932049976</v>
+        <v>-10.19911329532731</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>0.1664882232109188</v>
       </c>
       <c r="E74">
-        <v>-13.36514553856357</v>
+        <v>-15.80367897847997</v>
       </c>
       <c r="F74">
-        <v>-1.874136664241638</v>
+        <v>-1.320917292853808</v>
       </c>
       <c r="G74">
-        <v>-10.43999189931022</v>
+        <v>-9.378693899785125</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>0.9969393403999679</v>
       </c>
       <c r="E75">
-        <v>-14.67814940624354</v>
+        <v>-15.50056104230254</v>
       </c>
       <c r="F75">
-        <v>-1.80833861306987</v>
+        <v>-1.156143419293347</v>
       </c>
       <c r="G75">
-        <v>-9.109440609985121</v>
+        <v>-9.543310776725384</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>1.845113637212975</v>
       </c>
       <c r="E76">
-        <v>-14.81692902068261</v>
+        <v>-16.71624347508368</v>
       </c>
       <c r="F76">
-        <v>-1.714935218199809</v>
+        <v>-1.219286552939142</v>
       </c>
       <c r="G76">
-        <v>-9.063937161547839</v>
+        <v>-8.807075243701327</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>2.710192724959535</v>
       </c>
       <c r="E77">
-        <v>-15.2114813755489</v>
+        <v>-16.51904654594566</v>
       </c>
       <c r="F77">
-        <v>-1.874114298321762</v>
+        <v>-1.379283231687658</v>
       </c>
       <c r="G77">
-        <v>-9.018513166203498</v>
+        <v>-9.143400186126964</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>3.585802146471161</v>
       </c>
       <c r="E78">
-        <v>-15.57365514126035</v>
+        <v>-18.14235956652724</v>
       </c>
       <c r="F78">
-        <v>-1.928811397928614</v>
+        <v>-1.432196856276282</v>
       </c>
       <c r="G78">
-        <v>-9.173661882901442</v>
+        <v>-8.770457299491447</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>4.466774037553107</v>
       </c>
       <c r="E79">
-        <v>-16.72657292429517</v>
+        <v>-17.99129873057937</v>
       </c>
       <c r="F79">
-        <v>-1.93077794214286</v>
+        <v>-1.402595147137242</v>
       </c>
       <c r="G79">
-        <v>-8.537567041894798</v>
+        <v>-9.018715109481393</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>5.345332324150061</v>
       </c>
       <c r="E80">
-        <v>-17.23860295186845</v>
+        <v>-17.67422403751031</v>
       </c>
       <c r="F80">
-        <v>-2.100477288280366</v>
+        <v>-1.534013150489175</v>
       </c>
       <c r="G80">
-        <v>-7.722414724305593</v>
+        <v>-8.167835384432374</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>6.201924788324334</v>
       </c>
       <c r="E81">
-        <v>-17.96615664288879</v>
+        <v>-17.29748669939019</v>
       </c>
       <c r="F81">
-        <v>-1.875333655138683</v>
+        <v>-1.553255296888805</v>
       </c>
       <c r="G81">
-        <v>-7.705090639498587</v>
+        <v>-8.627200062370566</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>7.027024085534974</v>
       </c>
       <c r="E82">
-        <v>-17.68833476251821</v>
+        <v>-19.03949102371281</v>
       </c>
       <c r="F82">
-        <v>-2.005236574510896</v>
+        <v>-1.651762263327514</v>
       </c>
       <c r="G82">
-        <v>-6.810760004246633</v>
+        <v>-7.588175413233686</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>7.806243143800499</v>
       </c>
       <c r="E83">
-        <v>-19.48081798660433</v>
+        <v>-19.98007771747598</v>
       </c>
       <c r="F83">
-        <v>-1.870376704600331</v>
+        <v>-1.889767957132465</v>
       </c>
       <c r="G83">
-        <v>-7.521140176608983</v>
+        <v>-7.687293146679465</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>8.51766562658395</v>
       </c>
       <c r="E84">
-        <v>-20.06936111101121</v>
+        <v>-20.85184519174458</v>
       </c>
       <c r="F84">
-        <v>-2.026222434293419</v>
+        <v>-1.159062586020812</v>
       </c>
       <c r="G84">
-        <v>-7.590055803099991</v>
+        <v>-7.749511539544527</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>9.145937033790299</v>
       </c>
       <c r="E85">
-        <v>-20.41563540448173</v>
+        <v>-21.24325931412356</v>
       </c>
       <c r="F85">
-        <v>-2.026182672658084</v>
+        <v>-1.729050598743513</v>
       </c>
       <c r="G85">
-        <v>-6.990459726663812</v>
+        <v>-7.493523605720383</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>9.677496445777935</v>
       </c>
       <c r="E86">
-        <v>-22.19841410876941</v>
+        <v>-21.70487836904346</v>
       </c>
       <c r="F86">
-        <v>-1.895572327523881</v>
+        <v>-1.605297478969684</v>
       </c>
       <c r="G86">
-        <v>-7.232066650665363</v>
+        <v>-7.175946282683637</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>10.09415020980344</v>
       </c>
       <c r="E87">
-        <v>-21.45372014363004</v>
+        <v>-23.78895456295748</v>
       </c>
       <c r="F87">
-        <v>-1.846894145465771</v>
+        <v>-1.637255893369689</v>
       </c>
       <c r="G87">
-        <v>-6.530270722886343</v>
+        <v>-7.669674423319464</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>10.37943117366773</v>
       </c>
       <c r="E88">
-        <v>-24.22026454134403</v>
+        <v>-24.7779823431807</v>
       </c>
       <c r="F88">
-        <v>-2.010200151988471</v>
+        <v>-1.914221362863106</v>
       </c>
       <c r="G88">
-        <v>-7.049049761617834</v>
+        <v>-7.613689787704849</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>10.52798010827375</v>
       </c>
       <c r="E89">
-        <v>-25.29502991995448</v>
+        <v>-25.98862458439129</v>
       </c>
       <c r="F89">
-        <v>-2.091711504423942</v>
+        <v>-1.668921065709102</v>
       </c>
       <c r="G89">
-        <v>-7.176045599049815</v>
+        <v>-7.385417741135482</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>10.53234170191264</v>
       </c>
       <c r="E90">
-        <v>-27.35072616726243</v>
+        <v>-26.51919418455197</v>
       </c>
       <c r="F90">
-        <v>-1.921074446386466</v>
+        <v>-1.905786097600399</v>
       </c>
       <c r="G90">
-        <v>-6.916866299325814</v>
+        <v>-7.187370975339662</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>10.38536031751209</v>
       </c>
       <c r="E91">
-        <v>-28.60759959961733</v>
+        <v>-28.88632264631543</v>
       </c>
       <c r="F91">
-        <v>-1.806133499043618</v>
+        <v>-1.950808694309955</v>
       </c>
       <c r="G91">
-        <v>-6.698204766456952</v>
+        <v>-6.761492465531199</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>10.09584932453154</v>
       </c>
       <c r="E92">
-        <v>-29.89510815863412</v>
+        <v>-30.00169485135266</v>
       </c>
       <c r="F92">
-        <v>-2.104547885697723</v>
+        <v>-2.09029333943035</v>
       </c>
       <c r="G92">
-        <v>-6.451552571053552</v>
+        <v>-7.845199547811622</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>9.672677883820276</v>
       </c>
       <c r="E93">
-        <v>-31.77977073538337</v>
+        <v>-33.36421133508311</v>
       </c>
       <c r="F93">
-        <v>-1.604716793420321</v>
+        <v>-2.256364436343594</v>
       </c>
       <c r="G93">
-        <v>-6.100869792624095</v>
+        <v>-7.210624247207504</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>9.122524449547354</v>
       </c>
       <c r="E94">
-        <v>-33.18129947720229</v>
+        <v>-32.17842362346362</v>
       </c>
       <c r="F94">
-        <v>-1.694357743546867</v>
+        <v>-2.161867596501838</v>
       </c>
       <c r="G94">
-        <v>-6.838962541695684</v>
+        <v>-7.866943210913555</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>8.469907027031196</v>
       </c>
       <c r="E95">
-        <v>-35.34815617597653</v>
+        <v>-34.46240703820924</v>
       </c>
       <c r="F95">
-        <v>-1.939671294579315</v>
+        <v>-2.10940543214774</v>
       </c>
       <c r="G95">
-        <v>-6.849708572516159</v>
+        <v>-7.669220878580584</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>7.731168172310085</v>
       </c>
       <c r="E96">
-        <v>-35.34059362438371</v>
+        <v>-37.21279384066386</v>
       </c>
       <c r="F96">
-        <v>-1.702640589207459</v>
+        <v>-2.600428493831175</v>
       </c>
       <c r="G96">
-        <v>-7.210455409385</v>
+        <v>-7.826998168436709</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>6.934479495202045</v>
       </c>
       <c r="E97">
-        <v>-38.14918263902192</v>
+        <v>-38.23639425569864</v>
       </c>
       <c r="F97">
-        <v>-1.694087695773554</v>
+        <v>-2.36867117534554</v>
       </c>
       <c r="G97">
-        <v>-8.154169452446263</v>
+        <v>-8.525374302673663</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>6.079691675787823</v>
       </c>
       <c r="E98">
-        <v>-40.8651258681742</v>
+        <v>-40.69117812459157</v>
       </c>
       <c r="F98">
-        <v>-1.542235525329363</v>
+        <v>-2.667108756286924</v>
       </c>
       <c r="G98">
-        <v>-7.404473241259527</v>
+        <v>-8.684171240555884</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>5.222176916546706</v>
       </c>
       <c r="E99">
-        <v>-42.87628004514271</v>
+        <v>-42.38496099344351</v>
       </c>
       <c r="F99">
-        <v>-1.655084844980142</v>
+        <v>-2.627889701601381</v>
       </c>
       <c r="G99">
-        <v>-8.544171580245644</v>
+        <v>-8.325483563012469</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>4.32287528456567</v>
       </c>
       <c r="E100">
-        <v>-44.67758926506978</v>
+        <v>-44.8550737468524</v>
       </c>
       <c r="F100">
-        <v>-1.413730061765673</v>
+        <v>-3.234251326981008</v>
       </c>
       <c r="G100">
-        <v>-8.271280000897981</v>
+        <v>-9.510016620236934</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>3.463142067052396</v>
       </c>
       <c r="E101">
-        <v>-45.83138783629909</v>
+        <v>-46.59905701431637</v>
       </c>
       <c r="F101">
-        <v>-1.39964450244847</v>
+        <v>-2.879788773486085</v>
       </c>
       <c r="G101">
-        <v>-9.253158012935961</v>
+        <v>-9.156880727562877</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>2.523883059167545</v>
       </c>
       <c r="E102">
-        <v>-48.36401617338387</v>
+        <v>-48.07333569106851</v>
       </c>
       <c r="F102">
-        <v>-1.366757488189927</v>
+        <v>-3.165664162764014</v>
       </c>
       <c r="G102">
-        <v>-8.970093127146118</v>
+        <v>-9.858478022609541</v>
       </c>
     </row>
   </sheetData>
